--- a/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
+++ b/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -783,7 +783,7 @@
         <v>1150</v>
       </c>
       <c r="M4" t="n">
-        <v>810000</v>
+        <v>1260000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -797,27 +797,27 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v7</t>
+          <t>manual-100g-20261022-r2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>five-stars-v1</t>
+          <t>manual-final-reference-20261022</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>d5d60e1d60095de40f4f0e7d07f34fc3b8048d817bd18518b1814e0ef4364fd1</t>
+          <t>7a71fa7861b3e86107485e7224b53dfe4a9db591e22759e249ba2b1ff0f6aff8</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>pending_unity_reference</t>
+          <t>unity_reference_calibrated</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>771a35134b5be09511e87492fdaf3faef2b980093dc6ebb6cb5c72ef688de8b5</t>
+          <t>0135233bbe9cd3e5595063faf8ef222cfca1c0806565061d900f507fd56db4ce</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
+++ b/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>manual-100g-20261022-r2</t>
+          <t xml:space="preserve">tower-support-20261027-v1</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -807,17 +807,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7a71fa7861b3e86107485e7224b53dfe4a9db591e22759e249ba2b1ff0f6aff8</t>
+          <t xml:space="preserve">b9b18d12f0ad9a4801f0667f2deeefef2374a2ad47b905a57840b0c7e2953c1a</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>unity_reference_calibrated</t>
+          <t xml:space="preserve">pending_unity_reference</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0135233bbe9cd3e5595063faf8ef222cfca1c0806565061d900f507fd56db4ce</t>
+          <t xml:space="preserve">c9753588962f3525b9c7ccd900bfd14397071cb27d9160ead6e010731c3efd69</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
+++ b/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tower-support-20261027-v1</t>
+          <t>tower-support-20261027-v1</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -807,17 +807,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">b9b18d12f0ad9a4801f0667f2deeefef2374a2ad47b905a57840b0c7e2953c1a</t>
+          <t>b9b18d12f0ad9a4801f0667f2deeefef2374a2ad47b905a57840b0c7e2953c1a</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pending_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">c9753588962f3525b9c7ccd900bfd14397071cb27d9160ead6e010731c3efd69</t>
+          <t>33f735599e6d0c76fd0c501461c54b15fc82aec761eaccdfb0d62ffdf1fcbf34</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
+++ b/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>33f735599e6d0c76fd0c501461c54b15fc82aec761eaccdfb0d62ffdf1fcbf34</t>
+          <t>4771650a8965cdc77fe9087ea2f3489959795d676ffeec2fd19123c83ede046b</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
+++ b/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4771650a8965cdc77fe9087ea2f3489959795d676ffeec2fd19123c83ede046b</t>
+          <t>cc53b07447d712c7a82f654b5969f0c3a0b499c37995febf95a5f00345309053</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
+++ b/Luban/Config/Datas/Levels/L20/LevelRating.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>cc53b07447d712c7a82f654b5969f0c3a0b499c37995febf95a5f00345309053</t>
+          <t>622ae4d42e059b947b7b58e0d09d9875df81e3187682f658bd1e0791dd08b156</t>
         </is>
       </c>
     </row>
